--- a/3th course/МИЭП/lab4.xlsx
+++ b/3th course/МИЭП/lab4.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/antonkorolev/Documents/university/3th course/МИЭП/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{00659FD0-8702-3340-A876-5AFD84B1DBD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DB692AA-8C3B-1A45-9676-031577EBE031}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{7A80CD19-2343-0E4A-BAB7-7725E2C7197D}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="29400" windowHeight="16880" xr2:uid="{7A80CD19-2343-0E4A-BAB7-7725E2C7197D}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -40,7 +40,7 @@
   <metadataTypes count="1">
     <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
-  <futureMetadata name="XLRICHVALUE" count="9">
+  <futureMetadata name="XLRICHVALUE" count="14">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -104,8 +104,43 @@
         </ext>
       </extLst>
     </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="9"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="10"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="11"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="12"/>
+        </ext>
+      </extLst>
+    </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="13"/>
+        </ext>
+      </extLst>
+    </bk>
   </futureMetadata>
-  <valueMetadata count="9">
+  <valueMetadata count="14">
     <bk>
       <rc t="1" v="0"/>
     </bk>
@@ -133,12 +168,27 @@
     <bk>
       <rc t="1" v="8"/>
     </bk>
+    <bk>
+      <rc t="1" v="9"/>
+    </bk>
+    <bk>
+      <rc t="1" v="10"/>
+    </bk>
+    <bk>
+      <rc t="1" v="11"/>
+    </bk>
+    <bk>
+      <rc t="1" v="12"/>
+    </bk>
+    <bk>
+      <rc t="1" v="13"/>
+    </bk>
   </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="28">
   <si>
     <t>i</t>
   </si>
@@ -173,14 +223,146 @@
     </r>
   </si>
   <si>
-    <t>вариант 4 выбрать наиболее тесный фактор между расходами и ценой. Выбрать фактор благодаря вычислению фактора парной корреляции обоих факторов с откликом</t>
+    <t>Вычисление коэффициентов парной коррелляции</t>
+  </si>
+  <si>
+    <t>Расходы на рекламу (млн.р./год)</t>
+  </si>
+  <si>
+    <t>Цена (руб. за единицу)</t>
+  </si>
+  <si>
+    <t>Разница для факторов</t>
+  </si>
+  <si>
+    <t>Разница для отклика</t>
+  </si>
+  <si>
+    <t>Коэффициент парной коррелляции</t>
+  </si>
+  <si>
+    <t>Квадрат разницы для факторов</t>
+  </si>
+  <si>
+    <t>Квадрат разницы отклика</t>
+  </si>
+  <si>
+    <t>Так как коэффициент парной корреляции у расходов на рекламу больше, то поэтому он является более тесным фактором по сравнению с ценой</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Поворотные точки</t>
+  </si>
+  <si>
+    <t>Случайность ост. комп.</t>
+  </si>
+  <si>
+    <r>
+      <t>d &gt; d</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow (Основной текст)"/>
+        <charset val="204"/>
+      </rPr>
+      <t>2 (1,36) - следовательно автокорреляции нет</t>
+    </r>
+  </si>
+  <si>
+    <t>R / S (3,12 - 4,09)</t>
+  </si>
+  <si>
+    <t>Значение не попадает в интервал, следовательно гипотеза о нормальном распределении отвергается</t>
+  </si>
+  <si>
+    <t>Средняя относительная ошибка, %</t>
+  </si>
+  <si>
+    <t>Коэффициент эластичности</t>
+  </si>
+  <si>
+    <t>Средний прирост</t>
+  </si>
+  <si>
+    <r>
+      <t>x</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow (Основной текст)"/>
+        <charset val="204"/>
+      </rPr>
+      <t>17</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>x</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow (Основной текст)"/>
+        <charset val="204"/>
+      </rPr>
+      <t>18</t>
+    </r>
+  </si>
+  <si>
+    <t>Точечный прогноз</t>
+  </si>
+  <si>
+    <t>Интервальный прогноз</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">U </t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow (Основной текст)"/>
+        <charset val="204"/>
+      </rPr>
+      <t>17</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">U </t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow (Основной текст)"/>
+        <charset val="204"/>
+      </rPr>
+      <t>18</t>
+    </r>
+  </si>
+  <si>
+    <t>Модель имеет низкую точность</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -203,16 +385,83 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF0A0A0A"/>
+      <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <vertAlign val="subscript"/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow (Основной текст)"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <vertAlign val="subscript"/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow (Основной текст)"/>
+      <charset val="204"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -220,18 +469,218 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -248,6 +697,1061 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ru-RU"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="ru-RU"/>
+              <a:t>Фактические и прогнозируемые значения</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Фактические значения</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Лист1!$S$25:$S$42</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="18"/>
+                <c:pt idx="0">
+                  <c:v>126</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>137</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>148</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>191</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>274</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>370</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>432</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>445</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>367</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>367</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>321</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>307</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>331</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>345</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>364</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>384</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-9A53-4247-9D26-048576150385}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>Прогнозируемые значения</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Лист1!$T$25:$T$42</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="18"/>
+                <c:pt idx="0">
+                  <c:v>235.21945199999999</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>246.03870800000001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>232.51463799999999</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>298.78258299999999</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>292.02054800000002</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>312.30665399999998</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>379.92700600000001</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>434.02328799999998</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>448.899765</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>324.478317</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>297.43017600000002</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>269.029628</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>351.52645799999999</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>269.029628</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>259.56277899999998</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>258.21037200000001</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>259.74310000000003</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>261.27582799999999</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-9A53-4247-9D26-048576150385}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="103626303"/>
+        <c:axId val="103612415"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="103626303"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="103612415"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="103612415"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ru-RU"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="103626303"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ru-RU"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ru-RU"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>74284</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>66137</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>512793</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>161507</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="8" name="Диаграмма 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{506FCCE2-2447-87C1-2416-8D0CF8AA15F9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
@@ -291,7 +1795,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="9">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="14">
   <rv s="0">
     <v>0</v>
     <v>5</v>
@@ -328,6 +1832,26 @@
     <v>8</v>
     <v>5</v>
   </rv>
+  <rv s="0">
+    <v>9</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>10</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>11</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>12</v>
+    <v>5</v>
+  </rv>
+  <rv s="0">
+    <v>13</v>
+    <v>5</v>
+  </rv>
 </rvData>
 </file>
 
@@ -351,6 +1875,11 @@
   <rel r:id="rId7"/>
   <rel r:id="rId8"/>
   <rel r:id="rId9"/>
+  <rel r:id="rId10"/>
+  <rel r:id="rId11"/>
+  <rel r:id="rId12"/>
+  <rel r:id="rId13"/>
+  <rel r:id="rId14"/>
 </richValueRels>
 </file>
 
@@ -671,179 +2200,2238 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38A4A3F8-03B7-684D-A744-AD19CD898930}">
-  <dimension ref="A1:L17"/>
+  <dimension ref="A1:Y43"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="14" max="14" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="20.83203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17.5" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="18" x14ac:dyDescent="0.2">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:21" ht="18" x14ac:dyDescent="0.2">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="e" vm="1">
+      <c r="D1" s="17" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="E1" t="e" vm="2">
+      <c r="E1" s="8" t="e" vm="2">
         <v>#VALUE!</v>
       </c>
-      <c r="F1" t="e" vm="3">
+      <c r="F1" s="8" t="e" vm="3">
         <v>#VALUE!</v>
       </c>
-      <c r="G1" t="e" vm="4">
+      <c r="G1" s="8" t="e" vm="4">
         <v>#VALUE!</v>
       </c>
-      <c r="H1" t="e" vm="5">
+      <c r="H1" s="8" t="e" vm="5">
         <v>#VALUE!</v>
       </c>
-      <c r="I1" t="e" vm="6">
+      <c r="I1" s="8" t="e" vm="6">
         <v>#VALUE!</v>
       </c>
-      <c r="J1" t="e" vm="7">
+      <c r="J1" s="8" t="e" vm="7">
         <v>#VALUE!</v>
       </c>
-      <c r="K1" t="e" vm="8">
+      <c r="K1" s="8" t="e" vm="8">
         <v>#VALUE!</v>
       </c>
-      <c r="L1" t="e" vm="9">
+      <c r="L1" s="18" t="e" vm="9">
         <v>#VALUE!</v>
       </c>
+      <c r="N1" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="8" t="e" vm="10">
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q1" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="35" t="s">
+        <v>18</v>
+      </c>
+      <c r="S1" s="35"/>
+      <c r="T1" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="36"/>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A2">
+    <row r="2" spans="1:21" ht="19" x14ac:dyDescent="0.25">
+      <c r="A2" s="19">
         <v>1</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="2">
         <v>126</v>
       </c>
+      <c r="C2" s="20">
+        <v>4</v>
+      </c>
+      <c r="D2" s="21">
+        <f>INTERCEPT($B$2:$B$17,$C$2:$C$17) + SLOPE($B$2:$B$17,$C$2:$C$17)*C2</f>
+        <v>235.21945211202203</v>
+      </c>
+      <c r="E2">
+        <f>B2-D2</f>
+        <v>-109.21945211202203</v>
+      </c>
+      <c r="F2">
+        <f>E2^2</f>
+        <v>11928.888719650273</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J2">
+        <f>(ABS(E2)/B2)*100</f>
+        <v>86.682104850811143</v>
+      </c>
+      <c r="K2">
+        <f>C2-$C$18</f>
+        <v>-5.2937499999999993</v>
+      </c>
+      <c r="L2" s="11">
+        <f>K2^2</f>
+        <v>28.023789062499993</v>
+      </c>
+      <c r="N2" s="9">
+        <v>0</v>
+      </c>
+      <c r="O2" s="1" t="str">
+        <f>IF(SUM(N2:N17)&gt;(2*(16-2)/3-2*SQRT((16*16 - 29)/90)), "случайно", "не случайно")</f>
+        <v>случайно</v>
+      </c>
+      <c r="P2" s="6">
+        <f>H18/F18</f>
+        <v>3633.9907438531459</v>
+      </c>
+      <c r="Q2" s="1">
+        <f>(MAX(E2:E17) - MIN(E2:E17))/ STDEV(E2:E17)</f>
+        <v>2.9926831474497559</v>
+      </c>
+      <c r="R2" s="37"/>
+      <c r="S2" s="37"/>
+      <c r="T2" s="37"/>
+      <c r="U2" s="38"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A3">
+    <row r="3" spans="1:21" ht="19" x14ac:dyDescent="0.25">
+      <c r="A3" s="19">
         <v>2</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="2">
         <v>137</v>
       </c>
+      <c r="C3" s="20">
+        <v>4.8</v>
+      </c>
+      <c r="D3" s="21">
+        <f t="shared" ref="D3:D17" si="0">INTERCEPT($B$2:$B$17,$C$2:$C$17) + SLOPE($B$2:$B$17,$C$2:$C$17)*C3</f>
+        <v>246.038708463452</v>
+      </c>
+      <c r="E3">
+        <f t="shared" ref="E3:E17" si="1">B3-D3</f>
+        <v>-109.038708463452</v>
+      </c>
+      <c r="F3">
+        <f t="shared" ref="F3:F17" si="2">E3^2</f>
+        <v>11889.439943377678</v>
+      </c>
+      <c r="G3">
+        <f>F3-F2</f>
+        <v>-39.448776272594841</v>
+      </c>
+      <c r="H3">
+        <f>G3^2</f>
+        <v>1556.2059494052417</v>
+      </c>
+      <c r="I3">
+        <f>E3*E2</f>
+        <v>11909.147997380725</v>
+      </c>
+      <c r="J3">
+        <f t="shared" ref="J3:J17" si="3">(ABS(E3)/B3)*100</f>
+        <v>79.590298148505113</v>
+      </c>
+      <c r="K3">
+        <f t="shared" ref="K3:K17" si="4">C3-$C$18</f>
+        <v>-4.4937499999999995</v>
+      </c>
+      <c r="L3" s="11">
+        <f t="shared" ref="L3:L17" si="5">K3^2</f>
+        <v>20.193789062499995</v>
+      </c>
+      <c r="N3" s="10">
+        <f>IF(OR(AND(E3&gt;E2,E3&gt;E4),AND(E3&lt;E2,E3&lt;E4)),1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="P3" s="42" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q3" s="43" t="s">
+        <v>17</v>
+      </c>
+      <c r="R3">
+        <f>ABS(E2)/B2</f>
+        <v>0.86682104850811137</v>
+      </c>
+      <c r="S3" s="1">
+        <f>1/16 * (SUM(R3:R17))*100</f>
+        <v>26.689013970634996</v>
+      </c>
+      <c r="T3" s="39">
+        <f>SLOPE($B$2:$B$17,$C$2:$C$17) *C18/B18</f>
+        <v>0.40966169776370848</v>
+      </c>
+      <c r="U3" s="40"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A4">
+    <row r="4" spans="1:21" ht="19" x14ac:dyDescent="0.25">
+      <c r="A4" s="19">
         <v>3</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="2">
         <v>148</v>
       </c>
+      <c r="C4" s="20">
+        <v>3.8</v>
+      </c>
+      <c r="D4" s="21">
+        <f t="shared" si="0"/>
+        <v>232.51463802416453</v>
+      </c>
+      <c r="E4">
+        <f t="shared" si="1"/>
+        <v>-84.514638024164526</v>
+      </c>
+      <c r="F4">
+        <f t="shared" si="2"/>
+        <v>7142.7240403555561</v>
+      </c>
+      <c r="G4">
+        <f t="shared" ref="G4:G17" si="6">F4-F3</f>
+        <v>-4746.7159030221219</v>
+      </c>
+      <c r="H4">
+        <f t="shared" ref="H4:H17" si="7">G4^2</f>
+        <v>22531311.864003118</v>
+      </c>
+      <c r="I4">
+        <f t="shared" ref="I4:I17" si="8">E4*E3</f>
+        <v>9215.3669764110509</v>
+      </c>
+      <c r="J4">
+        <f t="shared" si="3"/>
+        <v>57.104485151462512</v>
+      </c>
+      <c r="K4">
+        <f t="shared" si="4"/>
+        <v>-5.4937499999999995</v>
+      </c>
+      <c r="L4" s="11">
+        <f t="shared" si="5"/>
+        <v>30.181289062499996</v>
+      </c>
+      <c r="N4" s="10">
+        <f t="shared" ref="N4:N16" si="9">IF(OR(AND(E4&gt;E3,E4&gt;E5),AND(E4&lt;E3,E4&lt;E5)),1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="P4" s="43"/>
+      <c r="Q4" s="43"/>
+      <c r="R4">
+        <f t="shared" ref="R4:R17" si="10">ABS(E3)/B3</f>
+        <v>0.79590298148505112</v>
+      </c>
+      <c r="S4" s="48" t="s">
+        <v>27</v>
+      </c>
+      <c r="U4" s="11"/>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A5">
+    <row r="5" spans="1:21" ht="19" x14ac:dyDescent="0.25">
+      <c r="A5" s="19">
         <v>4</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="2">
         <v>191</v>
       </c>
+      <c r="C5" s="20">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="D5" s="21">
+        <f t="shared" si="0"/>
+        <v>298.78258317667309</v>
+      </c>
+      <c r="E5">
+        <f t="shared" si="1"/>
+        <v>-107.78258317667309</v>
+      </c>
+      <c r="F5">
+        <f t="shared" si="2"/>
+        <v>11617.085236236451</v>
+      </c>
+      <c r="G5">
+        <f t="shared" si="6"/>
+        <v>4474.3611958808951</v>
+      </c>
+      <c r="H5">
+        <f t="shared" si="7"/>
+        <v>20019908.111204714</v>
+      </c>
+      <c r="I5">
+        <f t="shared" si="8"/>
+        <v>9109.2060024859311</v>
+      </c>
+      <c r="J5">
+        <f t="shared" si="3"/>
+        <v>56.430671820247689</v>
+      </c>
+      <c r="K5">
+        <f t="shared" si="4"/>
+        <v>-0.59375</v>
+      </c>
+      <c r="L5" s="11">
+        <f t="shared" si="5"/>
+        <v>0.3525390625</v>
+      </c>
+      <c r="N5" s="10">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="P5" s="43"/>
+      <c r="Q5" s="43"/>
+      <c r="R5">
+        <f t="shared" si="10"/>
+        <v>0.57104485151462514</v>
+      </c>
+      <c r="S5" s="48"/>
+      <c r="U5" s="11"/>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A6">
+    <row r="6" spans="1:21" ht="19" x14ac:dyDescent="0.25">
+      <c r="A6" s="19">
         <v>5</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="2">
         <v>274</v>
       </c>
+      <c r="C6" s="20">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="D6" s="21">
+        <f t="shared" si="0"/>
+        <v>292.02054795702935</v>
+      </c>
+      <c r="E6">
+        <f t="shared" si="1"/>
+        <v>-18.020547957029351</v>
+      </c>
+      <c r="F6">
+        <f t="shared" si="2"/>
+        <v>324.74014867159468</v>
+      </c>
+      <c r="G6">
+        <f t="shared" si="6"/>
+        <v>-11292.345087564856</v>
+      </c>
+      <c r="H6">
+        <f t="shared" si="7"/>
+        <v>127517057.57665013</v>
+      </c>
+      <c r="I6">
+        <f t="shared" si="8"/>
+        <v>1942.3012090677423</v>
+      </c>
+      <c r="J6">
+        <f t="shared" si="3"/>
+        <v>6.5768423200837045</v>
+      </c>
+      <c r="K6">
+        <f t="shared" si="4"/>
+        <v>-1.09375</v>
+      </c>
+      <c r="L6" s="11">
+        <f t="shared" si="5"/>
+        <v>1.1962890625</v>
+      </c>
+      <c r="N6" s="10">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="P6" s="43"/>
+      <c r="Q6" s="43"/>
+      <c r="R6">
+        <f t="shared" si="10"/>
+        <v>0.56430671820247691</v>
+      </c>
+      <c r="S6" s="48"/>
+      <c r="U6" s="11"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7">
+    <row r="7" spans="1:21" ht="19" x14ac:dyDescent="0.25">
+      <c r="A7" s="19">
         <v>6</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="2">
         <v>370</v>
       </c>
+      <c r="C7" s="20">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="D7" s="21">
+        <f t="shared" si="0"/>
+        <v>312.3066536159605</v>
+      </c>
+      <c r="E7">
+        <f t="shared" si="1"/>
+        <v>57.693346384039501</v>
+      </c>
+      <c r="F7">
+        <f t="shared" si="2"/>
+        <v>3328.5222169887638</v>
+      </c>
+      <c r="G7">
+        <f t="shared" si="6"/>
+        <v>3003.782068317169</v>
+      </c>
+      <c r="H7">
+        <f t="shared" si="7"/>
+        <v>9022706.7139437702</v>
+      </c>
+      <c r="I7">
+        <f t="shared" si="8"/>
+        <v>-1039.6657153150898</v>
+      </c>
+      <c r="J7">
+        <f t="shared" si="3"/>
+        <v>15.592796320010677</v>
+      </c>
+      <c r="K7">
+        <f t="shared" si="4"/>
+        <v>0.40625</v>
+      </c>
+      <c r="L7" s="11">
+        <f t="shared" si="5"/>
+        <v>0.1650390625</v>
+      </c>
+      <c r="N7" s="10">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="P7" s="43"/>
+      <c r="Q7" s="43"/>
+      <c r="R7">
+        <f t="shared" si="10"/>
+        <v>6.5768423200837048E-2</v>
+      </c>
+      <c r="S7" s="48"/>
+      <c r="U7" s="11"/>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A8">
+    <row r="8" spans="1:21" ht="19" x14ac:dyDescent="0.25">
+      <c r="A8" s="19">
         <v>7</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="2">
         <v>432</v>
       </c>
+      <c r="C8" s="20">
+        <v>14.7</v>
+      </c>
+      <c r="D8" s="21">
+        <f t="shared" si="0"/>
+        <v>379.92700581239785</v>
+      </c>
+      <c r="E8">
+        <f t="shared" si="1"/>
+        <v>52.072994187602148</v>
+      </c>
+      <c r="F8">
+        <f t="shared" si="2"/>
+        <v>2711.5967236620472</v>
+      </c>
+      <c r="G8">
+        <f t="shared" si="6"/>
+        <v>-616.92549332671661</v>
+      </c>
+      <c r="H8">
+        <f t="shared" si="7"/>
+        <v>380597.06431641267</v>
+      </c>
+      <c r="I8">
+        <f t="shared" si="8"/>
+        <v>3004.2652909194062</v>
+      </c>
+      <c r="J8">
+        <f t="shared" si="3"/>
+        <v>12.053933839722719</v>
+      </c>
+      <c r="K8">
+        <f t="shared" si="4"/>
+        <v>5.40625</v>
+      </c>
+      <c r="L8" s="11">
+        <f t="shared" si="5"/>
+        <v>29.2275390625</v>
+      </c>
+      <c r="N8" s="10">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="P8" s="43"/>
+      <c r="Q8" s="43"/>
+      <c r="R8">
+        <f t="shared" si="10"/>
+        <v>0.15592796320010677</v>
+      </c>
+      <c r="S8" s="48"/>
+      <c r="U8" s="11"/>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9">
+    <row r="9" spans="1:21" ht="19" x14ac:dyDescent="0.25">
+      <c r="A9" s="19">
         <v>8</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="2">
         <v>445</v>
       </c>
-      <c r="E9" t="s">
+      <c r="C9" s="20">
+        <v>18.7</v>
+      </c>
+      <c r="D9" s="21">
+        <f t="shared" si="0"/>
+        <v>434.02328756954762</v>
+      </c>
+      <c r="E9">
+        <f t="shared" si="1"/>
+        <v>10.97671243045238</v>
+      </c>
+      <c r="F9">
+        <f t="shared" si="2"/>
+        <v>120.48821578084781</v>
+      </c>
+      <c r="G9">
+        <f t="shared" si="6"/>
+        <v>-2591.1085078811993</v>
+      </c>
+      <c r="H9">
+        <f t="shared" si="7"/>
+        <v>6713843.2996143354</v>
+      </c>
+      <c r="I9">
+        <f t="shared" si="8"/>
+        <v>571.59028258992703</v>
+      </c>
+      <c r="J9">
+        <f t="shared" si="3"/>
+        <v>2.466676950663456</v>
+      </c>
+      <c r="K9">
+        <f t="shared" si="4"/>
+        <v>9.40625</v>
+      </c>
+      <c r="L9" s="11">
+        <f t="shared" si="5"/>
+        <v>88.4775390625</v>
+      </c>
+      <c r="N9" s="10">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="P9" s="43"/>
+      <c r="Q9" s="43"/>
+      <c r="R9">
+        <f t="shared" si="10"/>
+        <v>0.12053933839722719</v>
+      </c>
+      <c r="S9" s="48"/>
+      <c r="U9" s="11"/>
+    </row>
+    <row r="10" spans="1:21" ht="19" x14ac:dyDescent="0.25">
+      <c r="A10" s="19">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2">
+        <v>367</v>
+      </c>
+      <c r="C10" s="20">
+        <v>19.8</v>
+      </c>
+      <c r="D10" s="21">
+        <f t="shared" si="0"/>
+        <v>448.89976505276388</v>
+      </c>
+      <c r="E10">
+        <f t="shared" si="1"/>
+        <v>-81.899765052763883</v>
+      </c>
+      <c r="F10">
+        <f t="shared" si="2"/>
+        <v>6707.571515697924</v>
+      </c>
+      <c r="G10">
+        <f t="shared" si="6"/>
+        <v>6587.0832999170761</v>
+      </c>
+      <c r="H10">
+        <f t="shared" si="7"/>
+        <v>43389666.400046438</v>
+      </c>
+      <c r="I10">
+        <f t="shared" si="8"/>
+        <v>-898.99016910580281</v>
+      </c>
+      <c r="J10">
+        <f t="shared" si="3"/>
+        <v>22.316012275957462</v>
+      </c>
+      <c r="K10">
+        <f t="shared" si="4"/>
+        <v>10.506250000000001</v>
+      </c>
+      <c r="L10" s="11">
+        <f t="shared" si="5"/>
+        <v>110.38128906250003</v>
+      </c>
+      <c r="N10" s="10">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="P10" s="43"/>
+      <c r="Q10" s="43"/>
+      <c r="R10">
+        <f t="shared" si="10"/>
+        <v>2.4666769506634562E-2</v>
+      </c>
+      <c r="S10" s="48"/>
+      <c r="U10" s="11"/>
+    </row>
+    <row r="11" spans="1:21" ht="19" x14ac:dyDescent="0.25">
+      <c r="A11" s="19">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2">
+        <v>367</v>
+      </c>
+      <c r="C11" s="20">
+        <v>10.6</v>
+      </c>
+      <c r="D11" s="21">
+        <f t="shared" si="0"/>
+        <v>324.47831701131929</v>
+      </c>
+      <c r="E11">
+        <f t="shared" si="1"/>
+        <v>42.521682988680709</v>
+      </c>
+      <c r="F11">
+        <f t="shared" si="2"/>
+        <v>1808.0935241898585</v>
+      </c>
+      <c r="G11">
+        <f t="shared" si="6"/>
+        <v>-4899.4779915080653</v>
+      </c>
+      <c r="H11">
+        <f t="shared" si="7"/>
+        <v>24004884.589271907</v>
+      </c>
+      <c r="I11">
+        <f t="shared" si="8"/>
+        <v>-3482.5158464210567</v>
+      </c>
+      <c r="J11">
+        <f t="shared" si="3"/>
+        <v>11.586289642692291</v>
+      </c>
+      <c r="K11">
+        <f t="shared" si="4"/>
+        <v>1.3062500000000004</v>
+      </c>
+      <c r="L11" s="11">
+        <f t="shared" si="5"/>
+        <v>1.7062890625000009</v>
+      </c>
+      <c r="N11" s="10">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="P11" s="43"/>
+      <c r="Q11" s="43"/>
+      <c r="R11">
+        <f t="shared" si="10"/>
+        <v>0.22316012275957461</v>
+      </c>
+      <c r="S11" s="48"/>
+      <c r="U11" s="11"/>
+    </row>
+    <row r="12" spans="1:21" ht="19" x14ac:dyDescent="0.25">
+      <c r="A12" s="19">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2">
+        <v>321</v>
+      </c>
+      <c r="C12" s="20">
+        <v>8.6</v>
+      </c>
+      <c r="D12" s="21">
+        <f t="shared" si="0"/>
+        <v>297.43017613274435</v>
+      </c>
+      <c r="E12">
+        <f t="shared" si="1"/>
+        <v>23.56982386725565</v>
+      </c>
+      <c r="F12">
+        <f t="shared" si="2"/>
+        <v>555.53659713345405</v>
+      </c>
+      <c r="G12">
+        <f t="shared" si="6"/>
+        <v>-1252.5569270564044</v>
+      </c>
+      <c r="H12">
+        <f t="shared" si="7"/>
+        <v>1568898.855516983</v>
+      </c>
+      <c r="I12">
+        <f t="shared" si="8"/>
+        <v>1002.2285785824852</v>
+      </c>
+      <c r="J12">
+        <f t="shared" si="3"/>
+        <v>7.3426242577120409</v>
+      </c>
+      <c r="K12">
+        <f t="shared" si="4"/>
+        <v>-0.69374999999999964</v>
+      </c>
+      <c r="L12" s="11">
+        <f t="shared" si="5"/>
+        <v>0.48128906249999953</v>
+      </c>
+      <c r="N12" s="10">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="P12" s="43"/>
+      <c r="Q12" s="43"/>
+      <c r="R12">
+        <f t="shared" si="10"/>
+        <v>0.11586289642692291</v>
+      </c>
+      <c r="S12" s="48"/>
+      <c r="U12" s="11"/>
+    </row>
+    <row r="13" spans="1:21" ht="19" x14ac:dyDescent="0.25">
+      <c r="A13" s="19">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2">
+        <v>307</v>
+      </c>
+      <c r="C13" s="20">
+        <v>6.5</v>
+      </c>
+      <c r="D13" s="21">
+        <f t="shared" si="0"/>
+        <v>269.02962821024067</v>
+      </c>
+      <c r="E13">
+        <f t="shared" si="1"/>
+        <v>37.970371789759326</v>
+      </c>
+      <c r="F13">
+        <f t="shared" si="2"/>
+        <v>1441.7491338525508</v>
+      </c>
+      <c r="G13">
+        <f t="shared" si="6"/>
+        <v>886.21253671909676</v>
+      </c>
+      <c r="H13">
+        <f t="shared" si="7"/>
+        <v>785372.66023809637</v>
+      </c>
+      <c r="I13">
+        <f t="shared" si="8"/>
+        <v>894.95497525884002</v>
+      </c>
+      <c r="J13">
+        <f t="shared" si="3"/>
+        <v>12.368199280051897</v>
+      </c>
+      <c r="K13">
+        <f t="shared" si="4"/>
+        <v>-2.7937499999999993</v>
+      </c>
+      <c r="L13" s="11">
+        <f t="shared" si="5"/>
+        <v>7.8050390624999961</v>
+      </c>
+      <c r="N13" s="10">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="P13" s="43"/>
+      <c r="Q13" s="43"/>
+      <c r="R13">
+        <f t="shared" si="10"/>
+        <v>7.342624257712041E-2</v>
+      </c>
+      <c r="S13" s="48"/>
+      <c r="U13" s="11"/>
+    </row>
+    <row r="14" spans="1:21" ht="19" x14ac:dyDescent="0.25">
+      <c r="A14" s="19">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2">
+        <v>331</v>
+      </c>
+      <c r="C14" s="20">
+        <v>12.6</v>
+      </c>
+      <c r="D14" s="21">
+        <f t="shared" si="0"/>
+        <v>351.52645788989417</v>
+      </c>
+      <c r="E14">
+        <f t="shared" si="1"/>
+        <v>-20.526457889894175</v>
+      </c>
+      <c r="F14">
+        <f t="shared" si="2"/>
+        <v>421.33547350559883</v>
+      </c>
+      <c r="G14">
+        <f t="shared" si="6"/>
+        <v>-1020.4136603469519</v>
+      </c>
+      <c r="H14">
+        <f t="shared" si="7"/>
+        <v>1041244.0382226646</v>
+      </c>
+      <c r="I14">
+        <f t="shared" si="8"/>
+        <v>-779.39723760612048</v>
+      </c>
+      <c r="J14">
+        <f t="shared" si="3"/>
+        <v>6.2013467945299618</v>
+      </c>
+      <c r="K14">
+        <f t="shared" si="4"/>
+        <v>3.3062500000000004</v>
+      </c>
+      <c r="L14" s="11">
+        <f t="shared" si="5"/>
+        <v>10.931289062500003</v>
+      </c>
+      <c r="N14" s="10">
+        <f t="shared" si="9"/>
+        <v>1</v>
+      </c>
+      <c r="P14" s="43"/>
+      <c r="Q14" s="43"/>
+      <c r="R14">
+        <f t="shared" si="10"/>
+        <v>0.12368199280051898</v>
+      </c>
+      <c r="S14" s="48"/>
+      <c r="U14" s="11"/>
+    </row>
+    <row r="15" spans="1:21" ht="19" x14ac:dyDescent="0.25">
+      <c r="A15" s="19">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2">
+        <v>345</v>
+      </c>
+      <c r="C15" s="20">
+        <v>6.5</v>
+      </c>
+      <c r="D15" s="21">
+        <f t="shared" si="0"/>
+        <v>269.02962821024067</v>
+      </c>
+      <c r="E15">
+        <f t="shared" si="1"/>
+        <v>75.970371789759326</v>
+      </c>
+      <c r="F15">
+        <f t="shared" si="2"/>
+        <v>5771.4973898742601</v>
+      </c>
+      <c r="G15">
+        <f t="shared" si="6"/>
+        <v>5350.161916368661</v>
+      </c>
+      <c r="H15">
+        <f t="shared" si="7"/>
+        <v>28624232.531361584</v>
+      </c>
+      <c r="I15">
+        <f t="shared" si="8"/>
+        <v>-1559.4026374220991</v>
+      </c>
+      <c r="J15">
+        <f t="shared" si="3"/>
+        <v>22.020397620220095</v>
+      </c>
+      <c r="K15">
+        <f t="shared" si="4"/>
+        <v>-2.7937499999999993</v>
+      </c>
+      <c r="L15" s="11">
+        <f t="shared" si="5"/>
+        <v>7.8050390624999961</v>
+      </c>
+      <c r="N15" s="10">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="P15" s="43"/>
+      <c r="Q15" s="43"/>
+      <c r="R15">
+        <f t="shared" si="10"/>
+        <v>6.2013467945299619E-2</v>
+      </c>
+      <c r="S15" s="48"/>
+      <c r="U15" s="11"/>
+    </row>
+    <row r="16" spans="1:21" ht="19" x14ac:dyDescent="0.25">
+      <c r="A16" s="19">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2">
+        <v>364</v>
+      </c>
+      <c r="C16" s="20">
+        <v>5.8</v>
+      </c>
+      <c r="D16" s="21">
+        <f t="shared" si="0"/>
+        <v>259.56277890273947</v>
+      </c>
+      <c r="E16">
+        <f t="shared" si="1"/>
+        <v>104.43722109726053</v>
+      </c>
+      <c r="F16">
+        <f t="shared" si="2"/>
+        <v>10907.133150518081</v>
+      </c>
+      <c r="G16">
+        <f t="shared" si="6"/>
+        <v>5135.6357606438205</v>
+      </c>
+      <c r="H16">
+        <f t="shared" si="7"/>
+        <v>26374754.666003633</v>
+      </c>
+      <c r="I16">
+        <f t="shared" si="8"/>
+        <v>7934.1345154481787</v>
+      </c>
+      <c r="J16">
+        <f t="shared" si="3"/>
+        <v>28.691544257489159</v>
+      </c>
+      <c r="K16">
+        <f t="shared" si="4"/>
+        <v>-3.4937499999999995</v>
+      </c>
+      <c r="L16" s="11">
+        <f t="shared" si="5"/>
+        <v>12.206289062499996</v>
+      </c>
+      <c r="N16" s="10">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="P16" s="43"/>
+      <c r="Q16" s="43"/>
+      <c r="R16">
+        <f t="shared" si="10"/>
+        <v>0.22020397620220095</v>
+      </c>
+      <c r="S16" s="48"/>
+      <c r="U16" s="11"/>
+    </row>
+    <row r="17" spans="1:25" ht="19" x14ac:dyDescent="0.25">
+      <c r="A17" s="22">
+        <v>16</v>
+      </c>
+      <c r="B17" s="23">
+        <v>384</v>
+      </c>
+      <c r="C17" s="24">
+        <v>5.7</v>
+      </c>
+      <c r="D17" s="25">
+        <f t="shared" si="0"/>
+        <v>258.21037185881073</v>
+      </c>
+      <c r="E17" s="13">
+        <f t="shared" si="1"/>
+        <v>125.78962814118927</v>
+      </c>
+      <c r="F17" s="13">
+        <f t="shared" si="2"/>
+        <v>15823.030547898676</v>
+      </c>
+      <c r="G17" s="13">
+        <f t="shared" si="6"/>
+        <v>4915.8973973805951</v>
+      </c>
+      <c r="H17" s="13">
+        <f t="shared" si="7"/>
+        <v>24166047.221573308</v>
+      </c>
+      <c r="I17" s="13">
+        <f t="shared" si="8"/>
+        <v>13137.119205923569</v>
+      </c>
+      <c r="J17" s="13">
+        <f t="shared" si="3"/>
+        <v>32.757715661768039</v>
+      </c>
+      <c r="K17" s="13">
+        <f t="shared" si="4"/>
+        <v>-3.5937499999999991</v>
+      </c>
+      <c r="L17" s="14">
+        <f t="shared" si="5"/>
+        <v>12.915039062499993</v>
+      </c>
+      <c r="N17" s="12">
+        <v>0</v>
+      </c>
+      <c r="O17" s="13"/>
+      <c r="P17" s="44"/>
+      <c r="Q17" s="44"/>
+      <c r="R17" s="13">
+        <f t="shared" si="10"/>
+        <v>0.2869154425748916</v>
+      </c>
+      <c r="S17" s="50"/>
+      <c r="T17" s="13"/>
+      <c r="U17" s="14"/>
+    </row>
+    <row r="18" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A18" s="2"/>
+      <c r="B18" s="4">
+        <f>AVERAGE(B2:B17)</f>
+        <v>306.8125</v>
+      </c>
+      <c r="C18" s="1">
+        <f>AVERAGE(C2:C17)</f>
+        <v>9.2937499999999993</v>
+      </c>
+      <c r="F18" s="1">
+        <f>SUM(F2:F17)</f>
+        <v>92499.432577393614</v>
+      </c>
+      <c r="H18" s="1">
+        <f>SUM(H3:H17)</f>
+        <v>336142081.79791653</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25" ht="18" x14ac:dyDescent="0.25">
+      <c r="A19" s="39" t="s">
         <v>3</v>
       </c>
+      <c r="B19" s="39"/>
+      <c r="C19" s="39"/>
+      <c r="D19" s="39"/>
+      <c r="E19" s="43" t="s">
+        <v>6</v>
+      </c>
+      <c r="F19" s="43"/>
+      <c r="G19" s="43" t="s">
+        <v>7</v>
+      </c>
+      <c r="H19" s="43"/>
+      <c r="I19" s="43" t="e" vm="11">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J19" s="43"/>
+      <c r="K19" s="41" t="e" vm="12">
+        <v>#VALUE!</v>
+      </c>
+      <c r="L19" s="41"/>
+      <c r="M19" s="43" t="s">
+        <v>9</v>
+      </c>
+      <c r="N19" s="43"/>
+      <c r="O19" s="43" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>20</v>
+      </c>
+      <c r="R19" t="s">
+        <v>21</v>
+      </c>
+      <c r="S19" t="s">
+        <v>22</v>
+      </c>
+      <c r="T19" s="41" t="s">
+        <v>23</v>
+      </c>
+      <c r="U19" s="41"/>
+      <c r="V19" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="W19" s="41"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A10">
+    <row r="20" spans="1:25" ht="18" x14ac:dyDescent="0.25">
+      <c r="A20" s="45" t="s">
+        <v>4</v>
+      </c>
+      <c r="B20" s="45"/>
+      <c r="C20" s="46" t="s">
+        <v>5</v>
+      </c>
+      <c r="D20" s="46"/>
+      <c r="E20" s="43"/>
+      <c r="F20" s="43"/>
+      <c r="G20" s="43"/>
+      <c r="H20" s="43"/>
+      <c r="I20" s="43"/>
+      <c r="J20" s="43"/>
+      <c r="K20" s="41"/>
+      <c r="L20" s="41"/>
+      <c r="M20" s="43"/>
+      <c r="N20" s="43"/>
+      <c r="O20" s="43"/>
+      <c r="Q20">
+        <f>(C17-C2)/15</f>
+        <v>0.11333333333333334</v>
+      </c>
+      <c r="R20">
+        <f>C17+Q20</f>
+        <v>5.8133333333333335</v>
+      </c>
+      <c r="S20">
+        <f>R20+Q20</f>
+        <v>5.9266666666666667</v>
+      </c>
+      <c r="T20" t="e" vm="13">
+        <v>#VALUE!</v>
+      </c>
+      <c r="U20">
+        <f>INTERCEPT($B$2:$B$17,$C$2:$C$17) + SLOPE($B$2:$B$17,$C$2:$C$17)*R20</f>
+        <v>259.74309984192996</v>
+      </c>
+      <c r="V20" t="s">
+        <v>25</v>
+      </c>
+      <c r="W20">
+        <f>U20+Y20</f>
+        <v>265.0954827534436</v>
+      </c>
+      <c r="X20">
+        <f>U20-Y20</f>
+        <v>254.39071693041632</v>
+      </c>
+      <c r="Y20">
+        <f>Q2*1.7084 *SQRT(1+1/16 + ((R20 - C18)^2)/M38)</f>
+        <v>5.3523829115136561</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25" ht="18" x14ac:dyDescent="0.25">
+      <c r="A21" s="45"/>
+      <c r="B21" s="45"/>
+      <c r="C21" s="46"/>
+      <c r="D21" s="46"/>
+      <c r="E21" s="43"/>
+      <c r="F21" s="43"/>
+      <c r="G21" s="43"/>
+      <c r="H21" s="43"/>
+      <c r="I21" s="43"/>
+      <c r="J21" s="43"/>
+      <c r="K21" s="41"/>
+      <c r="L21" s="41"/>
+      <c r="M21" s="43"/>
+      <c r="N21" s="43"/>
+      <c r="O21" s="43"/>
+      <c r="T21" t="e" vm="14">
+        <v>#VALUE!</v>
+      </c>
+      <c r="U21">
+        <f>INTERCEPT($B$2:$B$17,$C$2:$C$17) + SLOPE($B$2:$B$17,$C$2:$C$17)*S20</f>
+        <v>261.27582782504919</v>
+      </c>
+      <c r="V21" t="s">
+        <v>26</v>
+      </c>
+      <c r="W21">
+        <f>U21+Y21</f>
+        <v>266.62297403484058</v>
+      </c>
+      <c r="X21">
+        <f>U21-Y21</f>
+        <v>255.9286816152578</v>
+      </c>
+      <c r="Y21">
+        <f>Q2*1.7084 *SQRT(1+1/16 + ((S20 - C18)^2)/M38)</f>
+        <v>5.3471462097913891</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A22" s="41">
+        <v>4</v>
+      </c>
+      <c r="B22" s="41"/>
+      <c r="C22" s="41">
+        <v>15</v>
+      </c>
+      <c r="D22" s="41"/>
+      <c r="E22">
+        <f>A22-$A$38</f>
+        <v>-5.2937499999999993</v>
+      </c>
+      <c r="F22">
+        <f>C22-$C$38</f>
+        <v>-0.65000000000000036</v>
+      </c>
+      <c r="G22" s="41">
+        <f>B2-$B$18</f>
+        <v>-180.8125</v>
+      </c>
+      <c r="H22" s="41"/>
+      <c r="I22">
+        <f>E22*G22</f>
+        <v>957.17617187499991</v>
+      </c>
+      <c r="J22">
+        <f>F22*G22</f>
+        <v>117.52812500000006</v>
+      </c>
+      <c r="K22" s="48" t="s">
+        <v>4</v>
+      </c>
+      <c r="L22" s="48" t="s">
+        <v>5</v>
+      </c>
+      <c r="M22">
+        <f>E22^2</f>
+        <v>28.023789062499993</v>
+      </c>
+      <c r="N22">
+        <f>F22^2</f>
+        <v>0.42250000000000049</v>
+      </c>
+      <c r="O22">
+        <f>G22^2</f>
+        <v>32693.16015625</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A23" s="41">
+        <v>4.8</v>
+      </c>
+      <c r="B23" s="41"/>
+      <c r="C23" s="41">
+        <v>14.8</v>
+      </c>
+      <c r="D23" s="41"/>
+      <c r="E23">
+        <f t="shared" ref="E23:E37" si="11">A23-$A$38</f>
+        <v>-4.4937499999999995</v>
+      </c>
+      <c r="F23">
+        <f t="shared" ref="F23:F37" si="12">C23-$C$38</f>
+        <v>-0.84999999999999964</v>
+      </c>
+      <c r="G23" s="41">
+        <f t="shared" ref="G23:G36" si="13">B3-$B$18</f>
+        <v>-169.8125</v>
+      </c>
+      <c r="H23" s="41"/>
+      <c r="I23">
+        <f t="shared" ref="I23:I37" si="14">E23*G23</f>
+        <v>763.09492187499995</v>
+      </c>
+      <c r="J23">
+        <f t="shared" ref="J23:J37" si="15">F23*G23</f>
+        <v>144.34062499999993</v>
+      </c>
+      <c r="K23" s="48"/>
+      <c r="L23" s="48"/>
+      <c r="M23">
+        <f t="shared" ref="M23:M37" si="16">E23^2</f>
+        <v>20.193789062499995</v>
+      </c>
+      <c r="N23">
+        <f t="shared" ref="N23:N37" si="17">F23^2</f>
+        <v>0.72249999999999936</v>
+      </c>
+      <c r="O23">
+        <f t="shared" ref="O23:O37" si="18">G23^2</f>
+        <v>28836.28515625</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A24" s="41">
+        <v>3.8</v>
+      </c>
+      <c r="B24" s="41"/>
+      <c r="C24" s="41">
+        <v>15.2</v>
+      </c>
+      <c r="D24" s="41"/>
+      <c r="E24">
+        <f t="shared" si="11"/>
+        <v>-5.4937499999999995</v>
+      </c>
+      <c r="F24">
+        <f t="shared" si="12"/>
+        <v>-0.45000000000000107</v>
+      </c>
+      <c r="G24" s="41">
+        <f t="shared" si="13"/>
+        <v>-158.8125</v>
+      </c>
+      <c r="H24" s="41"/>
+      <c r="I24">
+        <f t="shared" si="14"/>
+        <v>872.47617187499986</v>
+      </c>
+      <c r="J24">
+        <f t="shared" si="15"/>
+        <v>71.465625000000173</v>
+      </c>
+      <c r="K24" s="48"/>
+      <c r="L24" s="48"/>
+      <c r="M24">
+        <f t="shared" si="16"/>
+        <v>30.181289062499996</v>
+      </c>
+      <c r="N24">
+        <f t="shared" si="17"/>
+        <v>0.20250000000000096</v>
+      </c>
+      <c r="O24">
+        <f t="shared" si="18"/>
+        <v>25221.41015625</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A25" s="41">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="B25" s="41"/>
+      <c r="C25" s="41">
+        <v>15.5</v>
+      </c>
+      <c r="D25" s="41"/>
+      <c r="E25">
+        <f t="shared" si="11"/>
+        <v>-0.59375</v>
+      </c>
+      <c r="F25">
+        <f t="shared" si="12"/>
+        <v>-0.15000000000000036</v>
+      </c>
+      <c r="G25" s="41">
+        <f t="shared" si="13"/>
+        <v>-115.8125</v>
+      </c>
+      <c r="H25" s="41"/>
+      <c r="I25">
+        <f t="shared" si="14"/>
+        <v>68.763671875</v>
+      </c>
+      <c r="J25">
+        <f t="shared" si="15"/>
+        <v>17.371875000000042</v>
+      </c>
+      <c r="K25" s="48"/>
+      <c r="L25" s="48"/>
+      <c r="M25">
+        <f t="shared" si="16"/>
+        <v>0.3525390625</v>
+      </c>
+      <c r="N25">
+        <f t="shared" si="17"/>
+        <v>2.2500000000000107E-2</v>
+      </c>
+      <c r="O25">
+        <f t="shared" si="18"/>
+        <v>13412.53515625</v>
+      </c>
+      <c r="R25" s="28">
+        <v>1</v>
+      </c>
+      <c r="S25" s="29">
+        <v>126</v>
+      </c>
+      <c r="T25" s="30">
+        <v>235.21945199999999</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A26" s="41">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="B26" s="41"/>
+      <c r="C26" s="41">
+        <v>15.5</v>
+      </c>
+      <c r="D26" s="41"/>
+      <c r="E26">
+        <f t="shared" si="11"/>
+        <v>-1.09375</v>
+      </c>
+      <c r="F26">
+        <f t="shared" si="12"/>
+        <v>-0.15000000000000036</v>
+      </c>
+      <c r="G26" s="41">
+        <f t="shared" si="13"/>
+        <v>-32.8125</v>
+      </c>
+      <c r="H26" s="41"/>
+      <c r="I26">
+        <f t="shared" si="14"/>
+        <v>35.888671875</v>
+      </c>
+      <c r="J26">
+        <f t="shared" si="15"/>
+        <v>4.9218750000000115</v>
+      </c>
+      <c r="K26" s="48"/>
+      <c r="L26" s="48"/>
+      <c r="M26">
+        <f t="shared" si="16"/>
+        <v>1.1962890625</v>
+      </c>
+      <c r="N26">
+        <f t="shared" si="17"/>
+        <v>2.2500000000000107E-2</v>
+      </c>
+      <c r="O26">
+        <f t="shared" si="18"/>
+        <v>1076.66015625</v>
+      </c>
+      <c r="R26" s="26">
+        <v>2</v>
+      </c>
+      <c r="S26" s="20">
+        <v>137</v>
+      </c>
+      <c r="T26" s="31">
+        <v>246.03870800000001</v>
+      </c>
+    </row>
+    <row r="27" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A27" s="41">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="B27" s="41"/>
+      <c r="C27" s="41">
+        <v>16</v>
+      </c>
+      <c r="D27" s="41"/>
+      <c r="E27">
+        <f t="shared" si="11"/>
+        <v>0.40625</v>
+      </c>
+      <c r="F27">
+        <f t="shared" si="12"/>
+        <v>0.34999999999999964</v>
+      </c>
+      <c r="G27" s="41">
+        <f t="shared" si="13"/>
+        <v>63.1875</v>
+      </c>
+      <c r="H27" s="41"/>
+      <c r="I27">
+        <f t="shared" si="14"/>
+        <v>25.669921875</v>
+      </c>
+      <c r="J27">
+        <f t="shared" si="15"/>
+        <v>22.115624999999977</v>
+      </c>
+      <c r="K27" s="48"/>
+      <c r="L27" s="48"/>
+      <c r="M27">
+        <f t="shared" si="16"/>
+        <v>0.1650390625</v>
+      </c>
+      <c r="N27">
+        <f t="shared" si="17"/>
+        <v>0.12249999999999975</v>
+      </c>
+      <c r="O27">
+        <f t="shared" si="18"/>
+        <v>3992.66015625</v>
+      </c>
+      <c r="R27" s="26">
+        <v>3</v>
+      </c>
+      <c r="S27" s="20">
+        <v>148</v>
+      </c>
+      <c r="T27" s="31">
+        <v>232.51463799999999</v>
+      </c>
+    </row>
+    <row r="28" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A28" s="41">
+        <v>14.7</v>
+      </c>
+      <c r="B28" s="41"/>
+      <c r="C28" s="41">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="D28" s="41"/>
+      <c r="E28">
+        <f>A28-$A$38</f>
+        <v>5.40625</v>
+      </c>
+      <c r="F28">
+        <f t="shared" si="12"/>
+        <v>2.4500000000000011</v>
+      </c>
+      <c r="G28" s="41">
+        <f t="shared" si="13"/>
+        <v>125.1875</v>
+      </c>
+      <c r="H28" s="41"/>
+      <c r="I28">
+        <f t="shared" si="14"/>
+        <v>676.794921875</v>
+      </c>
+      <c r="J28">
+        <f t="shared" si="15"/>
+        <v>306.70937500000014</v>
+      </c>
+      <c r="K28" s="48"/>
+      <c r="L28" s="48"/>
+      <c r="M28">
+        <f t="shared" si="16"/>
+        <v>29.2275390625</v>
+      </c>
+      <c r="N28">
+        <f t="shared" si="17"/>
+        <v>6.0025000000000048</v>
+      </c>
+      <c r="O28">
+        <f t="shared" si="18"/>
+        <v>15671.91015625</v>
+      </c>
+      <c r="R28" s="26">
+        <v>4</v>
+      </c>
+      <c r="S28" s="20">
+        <v>191</v>
+      </c>
+      <c r="T28" s="31">
+        <v>298.78258299999999</v>
+      </c>
+    </row>
+    <row r="29" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A29" s="41">
+        <v>18.7</v>
+      </c>
+      <c r="B29" s="41"/>
+      <c r="C29" s="41">
+        <v>13</v>
+      </c>
+      <c r="D29" s="41"/>
+      <c r="E29">
+        <f t="shared" si="11"/>
+        <v>9.40625</v>
+      </c>
+      <c r="F29">
+        <f t="shared" si="12"/>
+        <v>-2.6500000000000004</v>
+      </c>
+      <c r="G29" s="41">
+        <f t="shared" si="13"/>
+        <v>138.1875</v>
+      </c>
+      <c r="H29" s="41"/>
+      <c r="I29">
+        <f t="shared" si="14"/>
+        <v>1299.826171875</v>
+      </c>
+      <c r="J29">
+        <f t="shared" si="15"/>
+        <v>-366.19687500000003</v>
+      </c>
+      <c r="K29" s="48"/>
+      <c r="L29" s="48"/>
+      <c r="M29">
+        <f t="shared" si="16"/>
+        <v>88.4775390625</v>
+      </c>
+      <c r="N29">
+        <f t="shared" si="17"/>
+        <v>7.0225000000000017</v>
+      </c>
+      <c r="O29">
+        <f t="shared" si="18"/>
+        <v>19095.78515625</v>
+      </c>
+      <c r="R29" s="26">
+        <v>5</v>
+      </c>
+      <c r="S29" s="20">
+        <v>274</v>
+      </c>
+      <c r="T29" s="31">
+        <v>292.02054800000002</v>
+      </c>
+    </row>
+    <row r="30" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A30" s="41">
+        <v>19.8</v>
+      </c>
+      <c r="B30" s="41"/>
+      <c r="C30" s="41">
+        <v>15.8</v>
+      </c>
+      <c r="D30" s="41"/>
+      <c r="E30">
+        <f t="shared" si="11"/>
+        <v>10.506250000000001</v>
+      </c>
+      <c r="F30">
+        <f t="shared" si="12"/>
+        <v>0.15000000000000036</v>
+      </c>
+      <c r="G30" s="41">
+        <f t="shared" si="13"/>
+        <v>60.1875</v>
+      </c>
+      <c r="H30" s="41"/>
+      <c r="I30">
+        <f t="shared" si="14"/>
+        <v>632.34492187500007</v>
+      </c>
+      <c r="J30">
+        <f t="shared" si="15"/>
+        <v>9.0281250000000206</v>
+      </c>
+      <c r="K30" s="48"/>
+      <c r="L30" s="48"/>
+      <c r="M30">
+        <f t="shared" si="16"/>
+        <v>110.38128906250003</v>
+      </c>
+      <c r="N30">
+        <f t="shared" si="17"/>
+        <v>2.2500000000000107E-2</v>
+      </c>
+      <c r="O30">
+        <f t="shared" si="18"/>
+        <v>3622.53515625</v>
+      </c>
+      <c r="R30" s="26">
+        <v>6</v>
+      </c>
+      <c r="S30" s="20">
+        <v>370</v>
+      </c>
+      <c r="T30" s="31">
+        <v>312.30665399999998</v>
+      </c>
+    </row>
+    <row r="31" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A31" s="41">
+        <v>10.6</v>
+      </c>
+      <c r="B31" s="41"/>
+      <c r="C31" s="41">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="D31" s="41"/>
+      <c r="E31">
+        <f t="shared" si="11"/>
+        <v>1.3062500000000004</v>
+      </c>
+      <c r="F31">
+        <f t="shared" si="12"/>
+        <v>1.2499999999999982</v>
+      </c>
+      <c r="G31" s="41">
+        <f t="shared" si="13"/>
+        <v>60.1875</v>
+      </c>
+      <c r="H31" s="41"/>
+      <c r="I31">
+        <f t="shared" si="14"/>
+        <v>78.619921875000017</v>
+      </c>
+      <c r="J31">
+        <f t="shared" si="15"/>
+        <v>75.234374999999886</v>
+      </c>
+      <c r="K31" s="48"/>
+      <c r="L31" s="48"/>
+      <c r="M31">
+        <f t="shared" si="16"/>
+        <v>1.7062890625000009</v>
+      </c>
+      <c r="N31">
+        <f t="shared" si="17"/>
+        <v>1.5624999999999956</v>
+      </c>
+      <c r="O31">
+        <f t="shared" si="18"/>
+        <v>3622.53515625</v>
+      </c>
+      <c r="R31" s="26">
+        <v>7</v>
+      </c>
+      <c r="S31" s="20">
+        <v>432</v>
+      </c>
+      <c r="T31" s="31">
+        <v>379.92700600000001</v>
+      </c>
+    </row>
+    <row r="32" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="A32" s="41">
+        <v>8.6</v>
+      </c>
+      <c r="B32" s="41"/>
+      <c r="C32" s="41">
+        <v>16.3</v>
+      </c>
+      <c r="D32" s="41"/>
+      <c r="E32">
+        <f t="shared" si="11"/>
+        <v>-0.69374999999999964</v>
+      </c>
+      <c r="F32">
+        <f t="shared" si="12"/>
+        <v>0.65000000000000036</v>
+      </c>
+      <c r="G32" s="41">
+        <f t="shared" si="13"/>
+        <v>14.1875</v>
+      </c>
+      <c r="H32" s="41"/>
+      <c r="I32">
+        <f t="shared" si="14"/>
+        <v>-9.8425781249999957</v>
+      </c>
+      <c r="J32">
+        <f t="shared" si="15"/>
+        <v>9.2218750000000043</v>
+      </c>
+      <c r="K32" s="48"/>
+      <c r="L32" s="48"/>
+      <c r="M32">
+        <f t="shared" si="16"/>
+        <v>0.48128906249999953</v>
+      </c>
+      <c r="N32">
+        <f t="shared" si="17"/>
+        <v>0.42250000000000049</v>
+      </c>
+      <c r="O32">
+        <f t="shared" si="18"/>
+        <v>201.28515625</v>
+      </c>
+      <c r="R32" s="26">
+        <v>8</v>
+      </c>
+      <c r="S32" s="20">
+        <v>445</v>
+      </c>
+      <c r="T32" s="31">
+        <v>434.02328799999998</v>
+      </c>
+    </row>
+    <row r="33" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A33" s="41">
+        <v>6.5</v>
+      </c>
+      <c r="B33" s="41"/>
+      <c r="C33" s="41">
+        <v>16.100000000000001</v>
+      </c>
+      <c r="D33" s="41"/>
+      <c r="E33">
+        <f t="shared" si="11"/>
+        <v>-2.7937499999999993</v>
+      </c>
+      <c r="F33">
+        <f t="shared" si="12"/>
+        <v>0.45000000000000107</v>
+      </c>
+      <c r="G33" s="41">
+        <f t="shared" si="13"/>
+        <v>0.1875</v>
+      </c>
+      <c r="H33" s="41"/>
+      <c r="I33">
+        <f t="shared" si="14"/>
+        <v>-0.52382812499999987</v>
+      </c>
+      <c r="J33">
+        <f t="shared" si="15"/>
+        <v>8.43750000000002E-2</v>
+      </c>
+      <c r="K33" s="48"/>
+      <c r="L33" s="48"/>
+      <c r="M33">
+        <f t="shared" si="16"/>
+        <v>7.8050390624999961</v>
+      </c>
+      <c r="N33">
+        <f t="shared" si="17"/>
+        <v>0.20250000000000096</v>
+      </c>
+      <c r="O33">
+        <f t="shared" si="18"/>
+        <v>3.515625E-2</v>
+      </c>
+      <c r="R33" s="26">
         <v>9</v>
       </c>
-      <c r="B10">
+      <c r="S33" s="20">
         <v>367</v>
       </c>
+      <c r="T33" s="31">
+        <v>448.899765</v>
+      </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A11">
+    <row r="34" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A34" s="41">
+        <v>12.6</v>
+      </c>
+      <c r="B34" s="41"/>
+      <c r="C34" s="41">
+        <v>15.4</v>
+      </c>
+      <c r="D34" s="41"/>
+      <c r="E34">
+        <f t="shared" si="11"/>
+        <v>3.3062500000000004</v>
+      </c>
+      <c r="F34">
+        <f t="shared" si="12"/>
+        <v>-0.25</v>
+      </c>
+      <c r="G34" s="41">
+        <f t="shared" si="13"/>
+        <v>24.1875</v>
+      </c>
+      <c r="H34" s="41"/>
+      <c r="I34">
+        <f t="shared" si="14"/>
+        <v>79.969921875000011</v>
+      </c>
+      <c r="J34">
+        <f t="shared" si="15"/>
+        <v>-6.046875</v>
+      </c>
+      <c r="K34" s="48"/>
+      <c r="L34" s="48"/>
+      <c r="M34">
+        <f t="shared" si="16"/>
+        <v>10.931289062500003</v>
+      </c>
+      <c r="N34">
+        <f t="shared" si="17"/>
+        <v>6.25E-2</v>
+      </c>
+      <c r="O34">
+        <f t="shared" si="18"/>
+        <v>585.03515625</v>
+      </c>
+      <c r="R34" s="26">
         <v>10</v>
       </c>
-      <c r="B11">
+      <c r="S34" s="20">
         <v>367</v>
       </c>
+      <c r="T34" s="31">
+        <v>324.478317</v>
+      </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A12">
+    <row r="35" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A35" s="41">
+        <v>6.5</v>
+      </c>
+      <c r="B35" s="41"/>
+      <c r="C35" s="41">
+        <v>15.7</v>
+      </c>
+      <c r="D35" s="41"/>
+      <c r="E35">
+        <f t="shared" si="11"/>
+        <v>-2.7937499999999993</v>
+      </c>
+      <c r="F35">
+        <f t="shared" si="12"/>
+        <v>4.9999999999998934E-2</v>
+      </c>
+      <c r="G35" s="41">
+        <f t="shared" si="13"/>
+        <v>38.1875</v>
+      </c>
+      <c r="H35" s="41"/>
+      <c r="I35">
+        <f t="shared" si="14"/>
+        <v>-106.68632812499997</v>
+      </c>
+      <c r="J35">
+        <f t="shared" si="15"/>
+        <v>1.9093749999999594</v>
+      </c>
+      <c r="K35" s="48"/>
+      <c r="L35" s="48"/>
+      <c r="M35">
+        <f t="shared" si="16"/>
+        <v>7.8050390624999961</v>
+      </c>
+      <c r="N35">
+        <f t="shared" si="17"/>
+        <v>2.4999999999998934E-3</v>
+      </c>
+      <c r="O35">
+        <f t="shared" si="18"/>
+        <v>1458.28515625</v>
+      </c>
+      <c r="R35" s="26">
         <v>11</v>
       </c>
-      <c r="B12">
+      <c r="S35" s="20">
         <v>321</v>
       </c>
+      <c r="T35" s="31">
+        <v>297.43017600000002</v>
+      </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A13">
+    <row r="36" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A36" s="41">
+        <v>5.8</v>
+      </c>
+      <c r="B36" s="41"/>
+      <c r="C36" s="41">
+        <v>16</v>
+      </c>
+      <c r="D36" s="41"/>
+      <c r="E36">
+        <f t="shared" si="11"/>
+        <v>-3.4937499999999995</v>
+      </c>
+      <c r="F36">
+        <f t="shared" si="12"/>
+        <v>0.34999999999999964</v>
+      </c>
+      <c r="G36" s="41">
+        <f t="shared" si="13"/>
+        <v>57.1875</v>
+      </c>
+      <c r="H36" s="41"/>
+      <c r="I36">
+        <f t="shared" si="14"/>
+        <v>-199.79882812499997</v>
+      </c>
+      <c r="J36">
+        <f t="shared" si="15"/>
+        <v>20.015624999999979</v>
+      </c>
+      <c r="K36" s="48"/>
+      <c r="L36" s="48"/>
+      <c r="M36">
+        <f t="shared" si="16"/>
+        <v>12.206289062499996</v>
+      </c>
+      <c r="N36">
+        <f t="shared" si="17"/>
+        <v>0.12249999999999975</v>
+      </c>
+      <c r="O36">
+        <f t="shared" si="18"/>
+        <v>3270.41015625</v>
+      </c>
+      <c r="R36" s="26">
         <v>12</v>
       </c>
-      <c r="B13">
+      <c r="S36" s="20">
         <v>307</v>
       </c>
+      <c r="T36" s="31">
+        <v>269.029628</v>
+      </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A14">
+    <row r="37" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A37" s="41">
+        <v>5.7</v>
+      </c>
+      <c r="B37" s="41"/>
+      <c r="C37" s="41">
+        <v>15.1</v>
+      </c>
+      <c r="D37" s="41"/>
+      <c r="E37">
+        <f t="shared" si="11"/>
+        <v>-3.5937499999999991</v>
+      </c>
+      <c r="F37">
+        <f t="shared" si="12"/>
+        <v>-0.55000000000000071</v>
+      </c>
+      <c r="G37" s="41">
+        <f>B17-$B$18</f>
+        <v>77.1875</v>
+      </c>
+      <c r="H37" s="41"/>
+      <c r="I37">
+        <f t="shared" si="14"/>
+        <v>-277.39257812499994</v>
+      </c>
+      <c r="J37">
+        <f t="shared" si="15"/>
+        <v>-42.453125000000057</v>
+      </c>
+      <c r="K37" s="48"/>
+      <c r="L37" s="48"/>
+      <c r="M37">
+        <f t="shared" si="16"/>
+        <v>12.915039062499993</v>
+      </c>
+      <c r="N37">
+        <f t="shared" si="17"/>
+        <v>0.30250000000000077</v>
+      </c>
+      <c r="O37">
+        <f t="shared" si="18"/>
+        <v>5957.91015625</v>
+      </c>
+      <c r="R37" s="26">
         <v>13</v>
       </c>
-      <c r="B14">
+      <c r="S37" s="20">
         <v>331</v>
       </c>
+      <c r="T37" s="31">
+        <v>351.52645799999999</v>
+      </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A15">
+    <row r="38" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A38" s="39">
+        <f>AVERAGE(A22:B37)</f>
+        <v>9.2937499999999993</v>
+      </c>
+      <c r="B38" s="39"/>
+      <c r="C38" s="39">
+        <f>AVERAGE(C22:D37)</f>
+        <v>15.65</v>
+      </c>
+      <c r="D38" s="39"/>
+      <c r="I38" s="1">
+        <f>SUM(I22:I37)</f>
+        <v>4896.3812499999995</v>
+      </c>
+      <c r="J38" s="1">
+        <f>SUM(J22:J37)</f>
+        <v>385.25000000000006</v>
+      </c>
+      <c r="K38" s="1">
+        <f>SQRT(M38*O38)</f>
+        <v>7580.4954388121332</v>
+      </c>
+      <c r="L38" s="1">
+        <f>SQRT(N38*O38)</f>
+        <v>1654.1783043251417</v>
+      </c>
+      <c r="M38" s="1">
+        <f>SUM(M22:M37)</f>
+        <v>362.049375</v>
+      </c>
+      <c r="N38" s="1">
+        <f t="shared" ref="N38:O38" si="19">SUM(N22:N37)</f>
+        <v>17.240000000000006</v>
+      </c>
+      <c r="O38" s="1">
+        <f t="shared" si="19"/>
+        <v>158718.4375</v>
+      </c>
+      <c r="R38" s="26">
         <v>14</v>
       </c>
-      <c r="B15">
+      <c r="S38" s="20">
         <v>345</v>
       </c>
+      <c r="T38" s="31">
+        <v>269.029628</v>
+      </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A16">
+    <row r="39" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A39" s="41" t="s">
+        <v>8</v>
+      </c>
+      <c r="B39" s="41"/>
+      <c r="C39" s="41"/>
+      <c r="D39" s="41"/>
+      <c r="R39" s="26">
         <v>15</v>
       </c>
-      <c r="B16">
+      <c r="S39" s="20">
         <v>364</v>
       </c>
+      <c r="T39" s="31">
+        <v>259.56277899999998</v>
+      </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A17">
+    <row r="40" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A40" s="47">
+        <f>I38/K38</f>
+        <v>0.64591836899347366</v>
+      </c>
+      <c r="B40" s="47"/>
+      <c r="C40" s="41">
+        <f>J38/L38</f>
+        <v>0.23289508693996036</v>
+      </c>
+      <c r="D40" s="41"/>
+      <c r="F40" s="49" t="s">
+        <v>11</v>
+      </c>
+      <c r="G40" s="49"/>
+      <c r="H40" s="49"/>
+      <c r="I40" s="49"/>
+      <c r="R40" s="27">
         <v>16</v>
       </c>
-      <c r="B17">
+      <c r="S40" s="24">
         <v>384</v>
       </c>
+      <c r="T40" s="32">
+        <v>258.21037200000001</v>
+      </c>
+    </row>
+    <row r="41" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="F41" s="49"/>
+      <c r="G41" s="49"/>
+      <c r="H41" s="49"/>
+      <c r="I41" s="49"/>
+      <c r="R41" s="33">
+        <v>17</v>
+      </c>
+      <c r="S41" s="5"/>
+      <c r="T41" s="34">
+        <v>259.74310000000003</v>
+      </c>
+    </row>
+    <row r="42" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="F42" s="49"/>
+      <c r="G42" s="49"/>
+      <c r="H42" s="49"/>
+      <c r="I42" s="49"/>
+      <c r="R42" s="27">
+        <v>18</v>
+      </c>
+      <c r="S42" s="13"/>
+      <c r="T42" s="32">
+        <v>261.27582799999999</v>
+      </c>
+    </row>
+    <row r="43" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="F43" s="49"/>
+      <c r="G43" s="49"/>
+      <c r="H43" s="49"/>
+      <c r="I43" s="49"/>
     </row>
   </sheetData>
+  <mergeCells count="73">
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="G33:H33"/>
+    <mergeCell ref="G34:H34"/>
+    <mergeCell ref="G35:H35"/>
+    <mergeCell ref="G36:H36"/>
+    <mergeCell ref="G37:H37"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="F40:I43"/>
+    <mergeCell ref="G26:H26"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C37:D37"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="G27:H27"/>
+    <mergeCell ref="G28:H28"/>
+    <mergeCell ref="G29:H29"/>
+    <mergeCell ref="G30:H30"/>
+    <mergeCell ref="G31:H31"/>
+    <mergeCell ref="G32:H32"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="P3:P17"/>
+    <mergeCell ref="Q3:Q17"/>
+    <mergeCell ref="R1:S2"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A20:B21"/>
+    <mergeCell ref="C20:D21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E19:F21"/>
+    <mergeCell ref="I19:J21"/>
+    <mergeCell ref="T1:U2"/>
+    <mergeCell ref="T3:U3"/>
+    <mergeCell ref="T19:U19"/>
+    <mergeCell ref="V19:W19"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="G22:H22"/>
+    <mergeCell ref="G23:H23"/>
+    <mergeCell ref="G24:H24"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="M19:N21"/>
+    <mergeCell ref="O19:O21"/>
+    <mergeCell ref="K22:K37"/>
+    <mergeCell ref="L22:L37"/>
+    <mergeCell ref="G19:H21"/>
+    <mergeCell ref="K19:L21"/>
+    <mergeCell ref="S4:S17"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>